--- a/install/无人机炫舞编程版本更新记录.xlsx
+++ b/install/无人机炫舞编程版本更新记录.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fly\UAVManage\install\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA3849C7-35F6-47E7-8521-1CF2E69B87CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F74AA01-9585-4501-ABE1-83E742B994F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5760" yWindow="525" windowWidth="20190" windowHeight="14955" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t>版本</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -343,6 +343,15 @@
   <si>
     <t>1、增加python编辑器中错误提示信息
 2、增加python编辑器中api函数高亮显示</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI4.3.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、音乐文件无法读取时软件可用继续使用
+2、修改启动参数判断功能</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -733,7 +742,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.375" customWidth="1"/>
@@ -1049,6 +1058,17 @@
         <v>56</v>
       </c>
     </row>
+    <row r="29" spans="1:3" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B29" s="3">
+        <v>45783</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/install/无人机炫舞编程版本更新记录.xlsx
+++ b/install/无人机炫舞编程版本更新记录.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fly\UAVManage\install\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F74AA01-9585-4501-ABE1-83E742B994F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4164F3B4-2E74-4CF1-AF4D-0434322C6986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="525" windowWidth="20190" windowHeight="14955" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
   <si>
     <t>版本</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -352,6 +352,24 @@
   <si>
     <t>1、音乐文件无法读取时软件可用继续使用
 2、修改启动参数判断功能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI4.3.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI4.3.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、与210版本地面站保持同步</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、修复5米地图配置文件错误
+2、三维仿真中增加圆环及二维码障碍物
+3、授权日期调整到2026年12月31日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -742,7 +760,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.375" customWidth="1"/>
@@ -1069,6 +1087,28 @@
         <v>58</v>
       </c>
     </row>
+    <row r="30" spans="1:3" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30" s="3">
+        <v>45819</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" s="3">
+        <v>45957</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/install/无人机炫舞编程版本更新记录.xlsx
+++ b/install/无人机炫舞编程版本更新记录.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fly\UAVManage\install\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4164F3B4-2E74-4CF1-AF4D-0434322C6986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B9E2616-4812-42E3-8ECB-3E125FFBE692}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="75" yWindow="390" windowWidth="24030" windowHeight="14955" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
   <si>
     <t>版本</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -370,6 +370,16 @@
     <t>1、修复5米地图配置文件错误
 2、三维仿真中增加圆环及二维码障碍物
 3、授权日期调整到2026年12月31日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI4.4.0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、P180增加比赛模式
+2、三维仿真中增加无人机摄像机视觉
+3、增加Blockly编程使用浏览器打开并编辑</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -760,7 +770,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.375" customWidth="1"/>
@@ -1109,6 +1119,17 @@
         <v>62</v>
       </c>
     </row>
+    <row r="32" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32" s="3">
+        <v>46041</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/install/无人机炫舞编程版本更新记录.xlsx
+++ b/install/无人机炫舞编程版本更新记录.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fly\UAVManage\install\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B9E2616-4812-42E3-8ECB-3E125FFBE692}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74944A84-E092-4E97-BB24-D731BF04857A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="75" yWindow="390" windowWidth="24030" windowHeight="14955" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -373,13 +373,20 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>AI4.4.0</t>
+    <t>AI5.1.0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>1、P180增加比赛模式
-2、三维仿真中增加无人机摄像机视觉
-3、增加Blockly编程使用浏览器打开并编辑</t>
+2、三维仿真中增加无人机摄像机可视图像
+3、增加Blockly编程使用浏览器打开并编辑
+4、比赛模式中增加导出项目功能
+5、增加拍照积木块
+6、调试模式增加显示识别地毯二维码ID
+7、增加提取拍照拓展内图片并转码成jpg
+8、增加3.2米二维码地毯素材
+9、增加AI识别积木块
+10、修改无人机传输协议</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1119,12 +1126,12 @@
         <v>62</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" ht="162" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B32" s="3">
-        <v>46041</v>
+        <v>46105</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>64</v>
